--- a/Summary Table.xlsx
+++ b/Summary Table.xlsx
@@ -1,21 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/vl22683_bristol_ac_uk/Documents/Documents/Misc/UNAIDS/FSW/Analysis/Analysis/Structural-Barriers-FSW-Review/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_0D75FDCE8F79A8D366075C52F3AD4A344E5EE418" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{917A0F4B-9289-4E1E-B6F6-F0BE628291F2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>dataframe</t>
+  </si>
+  <si>
+    <t>num_studies</t>
+  </si>
+  <si>
+    <t>num_estimates</t>
+  </si>
+  <si>
+    <t>total_exposed_num</t>
+  </si>
+  <si>
+    <t>total_sample_size</t>
+  </si>
+  <si>
+    <t>exposed_percentage</t>
+  </si>
+  <si>
+    <t>pooled_prev</t>
+  </si>
+  <si>
+    <t>pooled_prev_ci_lb</t>
+  </si>
+  <si>
+    <t>pooled_prev_ci_ub</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>fsw_data_pv_ever_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_pv_recent_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_sv_ever_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_sv_recent_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_psv_ever_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_psv_recent_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_other_ever_studies</t>
+  </si>
+  <si>
+    <t>fsw_data_other_recent_studies</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -25,6 +106,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,27 +137,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +206,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +240,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +275,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,332 +451,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dataframe</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>num_studies</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>num_estimates</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total_exposed_num</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_sample_size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>exposed_percentage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pooled_prev</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pooled_prev_ci_lb</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pooled_prev_ci_ub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>fsw_data_pv_ever_studies</t>
-        </is>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>22</v>
       </c>
       <c r="D2">
+        <v>13557</v>
+      </c>
+      <c r="E2">
+        <v>57809</v>
+      </c>
+      <c r="F2">
+        <v>23.451365704302098</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.21311535013310731</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.15121223610503379</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.29165257299336889</v>
+      </c>
+      <c r="J2">
+        <v>98.262927446185344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>11557</v>
+      </c>
+      <c r="E3">
+        <v>63206</v>
+      </c>
+      <c r="F3">
+        <v>18.284656519950641</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.15599600568290861</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1062888518136085</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.22314508686254719</v>
+      </c>
+      <c r="J3">
+        <v>98.776377079206981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>5080</v>
+      </c>
+      <c r="E4">
+        <v>24693</v>
+      </c>
+      <c r="F4">
+        <v>20.572631919977319</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.2187315203532624</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.16950056586211029</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.27748392999046972</v>
+      </c>
+      <c r="J4">
+        <v>96.149545786641468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>2306</v>
+      </c>
+      <c r="E5">
+        <v>5075</v>
+      </c>
+      <c r="F5">
+        <v>45.438423645320199</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.35407200077152279</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.24286476112399491</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.48367121497486282</v>
+      </c>
+      <c r="J5">
+        <v>96.682396620599562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
         <v>7177</v>
       </c>
-      <c r="E2">
+      <c r="E6">
         <v>21491</v>
       </c>
-      <c r="F2">
-        <v>33.39537480805919</v>
-      </c>
-      <c r="G2">
-        <v>0.3222687483912652</v>
-      </c>
-      <c r="H2">
-        <v>0.2571090532419761</v>
-      </c>
-      <c r="I2">
-        <v>0.3951581204788198</v>
-      </c>
-      <c r="J2">
+      <c r="F6">
+        <v>33.395374808059188</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.32226874839126518</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.25710905324197608</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.39515812047881982</v>
+      </c>
+      <c r="J6">
         <v>97.18517362720965</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fsw_data_pv_recent_studies</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>22</v>
-      </c>
-      <c r="D3">
-        <v>13557</v>
-      </c>
-      <c r="E3">
-        <v>57809</v>
-      </c>
-      <c r="F3">
-        <v>23.4513657043021</v>
-      </c>
-      <c r="G3">
-        <v>0.2131153501331073</v>
-      </c>
-      <c r="H3">
-        <v>0.1512122361050338</v>
-      </c>
-      <c r="I3">
-        <v>0.2916525729933689</v>
-      </c>
-      <c r="J3">
-        <v>98.26292744618534</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>fsw_data_sv_ever_studies</t>
-        </is>
-      </c>
-      <c r="B4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C7">
         <v>30</v>
       </c>
-      <c r="D4">
+      <c r="D7">
         <v>9167</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>39056</v>
       </c>
-      <c r="F4">
+      <c r="F7">
         <v>23.47142564522737</v>
       </c>
-      <c r="G4">
-        <v>0.2427991527180378</v>
-      </c>
-      <c r="H4">
-        <v>0.1911036420705323</v>
-      </c>
-      <c r="I4">
-        <v>0.3032364922316451</v>
-      </c>
-      <c r="J4">
-        <v>98.10195987637306</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>fsw_data_sv_recent_studies</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>26</v>
-      </c>
-      <c r="C5">
-        <v>30</v>
-      </c>
-      <c r="D5">
-        <v>11557</v>
-      </c>
-      <c r="E5">
-        <v>63206</v>
-      </c>
-      <c r="F5">
-        <v>18.28465651995064</v>
-      </c>
-      <c r="G5">
-        <v>0.1559960056829086</v>
-      </c>
-      <c r="H5">
-        <v>0.1062888518136085</v>
-      </c>
-      <c r="I5">
-        <v>0.2231450868625472</v>
-      </c>
-      <c r="J5">
-        <v>98.77637707920698</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>fsw_data_psv_ever_studies</t>
-        </is>
-      </c>
-      <c r="B6">
+      <c r="G7" s="2">
+        <v>0.24279915271803779</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.19110364207053229</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.30323649223164512</v>
+      </c>
+      <c r="J7">
+        <v>98.101959876373058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="D6">
-        <v>9012.816000000001</v>
-      </c>
-      <c r="E6">
+      <c r="D8">
+        <v>9012.8160000000007</v>
+      </c>
+      <c r="E8">
         <v>38109</v>
       </c>
-      <c r="F6">
-        <v>23.6500984019523</v>
-      </c>
-      <c r="G6">
-        <v>0.4863868628631939</v>
-      </c>
-      <c r="H6">
-        <v>0.3644978222144872</v>
-      </c>
-      <c r="I6">
-        <v>0.6099168993667249</v>
-      </c>
-      <c r="J6">
-        <v>99.23850963444769</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>fsw_data_psv_recent_studies</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>5080</v>
-      </c>
-      <c r="E7">
-        <v>24693</v>
-      </c>
-      <c r="F7">
-        <v>20.57263191997732</v>
-      </c>
-      <c r="G7">
-        <v>0.2187315203532624</v>
-      </c>
-      <c r="H7">
-        <v>0.1695005658621103</v>
-      </c>
-      <c r="I7">
-        <v>0.2774839299904697</v>
-      </c>
-      <c r="J7">
-        <v>96.14954578664147</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>fsw_data_other_ever_studies</t>
-        </is>
-      </c>
-      <c r="B8">
+      <c r="F8">
+        <v>23.650098401952299</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.48638686286319388</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.36449782221448718</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.60991689936672489</v>
+      </c>
+      <c r="J8">
+        <v>99.238509634447695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>1101</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>2477</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>44.44893015744853</v>
       </c>
-      <c r="G8">
-        <v>0.4743649347295331</v>
-      </c>
-      <c r="H8">
-        <v>0.3582199975121095</v>
-      </c>
-      <c r="I8">
+      <c r="G9" s="2">
+        <v>0.47436493472953312</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.35821999751210948</v>
+      </c>
+      <c r="I9" s="2">
         <v>0.593351489915939</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <v>94.28973682647792</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>fsw_data_other_recent_studies</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>2306</v>
-      </c>
-      <c r="E9">
-        <v>5075</v>
-      </c>
-      <c r="F9">
-        <v>45.4384236453202</v>
-      </c>
-      <c r="G9">
-        <v>0.3540720007715228</v>
-      </c>
-      <c r="H9">
-        <v>0.2428647611239949</v>
-      </c>
-      <c r="I9">
-        <v>0.4836712149748628</v>
-      </c>
-      <c r="J9">
-        <v>96.68239662059956</v>
       </c>
     </row>
   </sheetData>
